--- a/F_grouping/reference/因子經濟意義篩.xlsx
+++ b/F_grouping/reference/因子經濟意義篩.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1590D4BA-44ED-C142-A114-5042DA1028E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33487,7 +33487,7 @@
         <v>126</v>
       </c>
       <c r="D322" t="str">
-        <f t="shared" ref="D322:D385" si="11">B322&amp;"-"&amp;C322</f>
+        <f t="shared" ref="D322:D333" si="11">B322&amp;"-"&amp;C322</f>
         <v>V-强势股占比</v>
       </c>
       <c r="E322" t="s">
